--- a/02-VALUATION/M06/bus311-valuation-m06-l01-bond-practice.xlsx
+++ b/02-VALUATION/M06/bus311-valuation-m06-l01-bond-practice.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mailendicott-my.sharepoint.com/personal/bevitts_endicott_edu/Documents/BUS311 Corporate Finance/BME - FA25- Teaching Materials - Brealey/Chapter 6 - Valuing Bonds/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bethanyevittsair2/Documents/GitHub/BUS311-Corporate_Finance/02-VALUATION/M06/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="393" documentId="8_{6A5EA361-940B-441B-AF07-420D05EB2885}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4070EE7F-F4F5-41A6-A9C8-0C7ED21DDAE6}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25F124FF-BEA2-5749-802F-C981400DC924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{1435D9AC-6043-4EE1-9429-8F681581CEF4}"/>
+    <workbookView xWindow="1340" yWindow="1440" windowWidth="16000" windowHeight="19200" xr2:uid="{1435D9AC-6043-4EE1-9429-8F681581CEF4}"/>
   </bookViews>
   <sheets>
-    <sheet name="Yield#1" sheetId="4" r:id="rId1"/>
-    <sheet name="Yield #2" sheetId="7" r:id="rId2"/>
-    <sheet name="Coupon" sheetId="8" r:id="rId3"/>
-    <sheet name="Years to Maturity" sheetId="5" r:id="rId4"/>
-    <sheet name="Total Return-CapGain" sheetId="11" r:id="rId5"/>
-    <sheet name="Downgrade Scenario" sheetId="10" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="12" r:id="rId1"/>
+    <sheet name="Yield#1" sheetId="4" r:id="rId2"/>
+    <sheet name="Yield #2" sheetId="7" r:id="rId3"/>
+    <sheet name="Coupon" sheetId="8" r:id="rId4"/>
+    <sheet name="Years to Maturity" sheetId="5" r:id="rId5"/>
+    <sheet name="Total Return-CapGain" sheetId="11" r:id="rId6"/>
+    <sheet name="Downgrade Scenario" sheetId="10" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="59">
   <si>
     <t>Input area:</t>
   </si>
@@ -206,6 +207,18 @@
   </si>
   <si>
     <t>You purchased a 10-year bond with a 6.5% coupon  at a yield of 6.00%. Interest Rates expected to fall 50bps during the next year, before you sell the bond.  What is the capital gain on the transaction? What is the total return earned on the bond?</t>
+  </si>
+  <si>
+    <t>Basic Bond Features</t>
+  </si>
+  <si>
+    <t>Face/Par Value Compound Frequency</t>
+  </si>
+  <si>
+    <t>Inputs for the Problem</t>
+  </si>
+  <si>
+    <t>Coupon Payments Rate (Annual %)</t>
   </si>
 </sst>
 </file>
@@ -1152,24 +1165,54 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AD099E2-4BF4-724B-B394-B351D64DCE9D}">
+  <dimension ref="A1:A6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82DB5E7F-2487-4705-B9EE-53506D10F10F}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="45.28515625" customWidth="1"/>
-    <col min="2" max="2" width="19.85546875" customWidth="1"/>
-    <col min="5" max="5" width="34.28515625" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.33203125" customWidth="1"/>
+    <col min="2" max="2" width="19.83203125" customWidth="1"/>
+    <col min="5" max="5" width="34.33203125" customWidth="1"/>
+    <col min="6" max="6" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="54" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="70" t="s">
         <v>53</v>
       </c>
       <c r="B1" s="70"/>
       <c r="C1" s="70"/>
     </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
@@ -1179,14 +1222,14 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
       <c r="B5" s="20"/>
       <c r="C5" s="21"/>
@@ -1195,7 +1238,7 @@
       <c r="F5" s="56"/>
       <c r="G5" s="57"/>
     </row>
-    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>3</v>
       </c>
@@ -1210,7 +1253,7 @@
       <c r="F6" s="52"/>
       <c r="G6" s="59"/>
     </row>
-    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>4</v>
       </c>
@@ -1225,7 +1268,7 @@
       <c r="F7" s="63"/>
       <c r="G7" s="59"/>
     </row>
-    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>5</v>
       </c>
@@ -1240,7 +1283,7 @@
       <c r="F8" s="50"/>
       <c r="G8" s="59"/>
     </row>
-    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>6</v>
       </c>
@@ -1255,7 +1298,7 @@
       <c r="F9" s="54"/>
       <c r="G9" s="59"/>
     </row>
-    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>7</v>
       </c>
@@ -1268,7 +1311,7 @@
       <c r="F10" s="54"/>
       <c r="G10" s="59"/>
     </row>
-    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>8</v>
       </c>
@@ -1283,7 +1326,7 @@
       <c r="F11" s="54"/>
       <c r="G11" s="59"/>
     </row>
-    <row r="12" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="11"/>
@@ -1294,14 +1337,14 @@
       <c r="F12" s="61"/>
       <c r="G12" s="62"/>
     </row>
-    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>1</v>
       </c>
@@ -1310,21 +1353,21 @@
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="13"/>
       <c r="B16" s="13"/>
       <c r="C16" s="28"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="68" t="s">
         <v>39</v>
       </c>
@@ -1333,7 +1376,7 @@
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
     </row>
-    <row r="18" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="68" t="s">
         <v>40</v>
       </c>
@@ -1342,7 +1385,7 @@
       <c r="D18" s="2"/>
       <c r="E18" s="2"/>
     </row>
-    <row r="19" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="15" t="s">
         <v>10</v>
       </c>
@@ -1351,7 +1394,7 @@
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
     </row>
-    <row r="20" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="15" t="s">
         <v>11</v>
       </c>
@@ -1360,14 +1403,14 @@
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
     </row>
-    <row r="21" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="15"/>
       <c r="B21" s="31"/>
       <c r="C21" s="30"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="68" t="s">
         <v>12</v>
       </c>
@@ -1376,21 +1419,21 @@
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
     </row>
-    <row r="23" spans="1:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:5" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A23" s="17"/>
       <c r="B23" s="17"/>
       <c r="C23" s="32"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
     </row>
-    <row r="24" spans="1:5" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="B25" s="33"/>
     </row>
   </sheetData>
@@ -1401,25 +1444,25 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F7FEBA7A-5787-4FC1-A0FA-2191276537DA}">
   <dimension ref="A2:H22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="24" customWidth="1"/>
-    <col min="3" max="3" width="17.7109375" customWidth="1"/>
-    <col min="6" max="6" width="35.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" customWidth="1"/>
+    <col min="6" max="6" width="35.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8" ht="128.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="128.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="70" t="s">
         <v>37</v>
       </c>
       <c r="C2" s="70"/>
       <c r="D2" s="70"/>
     </row>
-    <row r="3" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="3" t="s">
         <v>38</v>
@@ -1431,7 +1474,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="2"/>
       <c r="B4" s="5"/>
       <c r="C4" s="20"/>
@@ -1441,7 +1484,7 @@
       <c r="G4" s="56"/>
       <c r="H4" s="57"/>
     </row>
-    <row r="5" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="2"/>
       <c r="B5" s="7" t="s">
         <v>17</v>
@@ -1457,7 +1500,7 @@
       <c r="G5" s="52"/>
       <c r="H5" s="59"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="7" t="s">
         <v>18</v>
@@ -1473,7 +1516,7 @@
       <c r="G6" s="53"/>
       <c r="H6" s="59"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="7" t="s">
         <v>13</v>
@@ -1489,7 +1532,7 @@
       <c r="G7" s="50"/>
       <c r="H7" s="59"/>
     </row>
-    <row r="8" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="7" t="s">
         <v>19</v>
@@ -1505,7 +1548,7 @@
       <c r="G8" s="51"/>
       <c r="H8" s="59"/>
     </row>
-    <row r="9" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="7" t="s">
         <v>7</v>
@@ -1521,7 +1564,7 @@
       <c r="G9" s="51"/>
       <c r="H9" s="59"/>
     </row>
-    <row r="10" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="7" t="s">
         <v>20</v>
@@ -1537,7 +1580,7 @@
       <c r="G10" s="54"/>
       <c r="H10" s="59"/>
     </row>
-    <row r="11" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
@@ -1549,14 +1592,14 @@
       <c r="G11" s="61"/>
       <c r="H11" s="62"/>
     </row>
-    <row r="12" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
     </row>
-    <row r="13" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="3" t="s">
         <v>1</v>
@@ -1566,7 +1609,7 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
     </row>
-    <row r="14" spans="1:8" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="3"/>
       <c r="C14" s="2"/>
@@ -1574,7 +1617,7 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -1582,7 +1625,7 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
     </row>
-    <row r="16" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="15" t="s">
         <v>14</v>
@@ -1592,7 +1635,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="15"/>
       <c r="C17" s="42"/>
@@ -1600,7 +1643,7 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
     </row>
-    <row r="18" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="15" t="s">
         <v>21</v>
@@ -1610,7 +1653,7 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
     </row>
-    <row r="19" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="15" t="s">
         <v>21</v>
@@ -1620,7 +1663,7 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
     </row>
-    <row r="20" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="15" t="s">
         <v>22</v>
@@ -1630,7 +1673,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" spans="1:6" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
       <c r="B21" s="17"/>
       <c r="C21" s="17"/>
@@ -1638,7 +1681,7 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
     </row>
-    <row r="22" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -1654,35 +1697,35 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{418EEFAF-5EFE-4F54-BC15-69D94EC2ACC4}">
   <dimension ref="A1:G24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="41" customWidth="1"/>
-    <col min="4" max="4" width="21.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>42</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>43</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3"/>
@@ -1691,7 +1734,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -1700,7 +1743,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="6"/>
       <c r="C7" s="7" t="s">
@@ -1711,7 +1754,7 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="6"/>
       <c r="C8" s="7" t="s">
@@ -1722,7 +1765,7 @@
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
-    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7" t="s">
@@ -1733,7 +1776,7 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
@@ -1744,7 +1787,7 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="2"/>
       <c r="B11" s="6"/>
       <c r="C11" s="7" t="s">
@@ -1755,7 +1798,7 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
       <c r="B12" s="9"/>
       <c r="C12" s="10"/>
@@ -1764,7 +1807,7 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
@@ -1773,7 +1816,7 @@
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3" t="s">
@@ -1784,7 +1827,7 @@
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
     </row>
-    <row r="15" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="3"/>
@@ -1793,7 +1836,7 @@
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
     </row>
-    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="12"/>
       <c r="C16" s="13"/>
@@ -1802,7 +1845,7 @@
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
     </row>
-    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="14"/>
       <c r="C17" s="15" t="s">
@@ -1813,7 +1856,7 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="14"/>
       <c r="C18" s="15" t="s">
@@ -1824,7 +1867,7 @@
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="2"/>
       <c r="B19" s="14"/>
       <c r="C19" s="15" t="s">
@@ -1835,7 +1878,7 @@
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="14"/>
       <c r="C20" s="15"/>
@@ -1844,7 +1887,7 @@
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
     </row>
-    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="14"/>
       <c r="C21" s="15" t="s">
@@ -1855,7 +1898,7 @@
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
     </row>
-    <row r="22" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
       <c r="B22" s="16"/>
       <c r="C22" s="17"/>
@@ -1864,7 +1907,7 @@
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
     </row>
-    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -1873,7 +1916,7 @@
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="D24" s="49"/>
     </row>
   </sheetData>
@@ -1881,35 +1924,35 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F41E8A6-715D-4EC4-9DF6-50B7CF44AA6C}">
   <dimension ref="A1:G20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="22.5703125" customWidth="1"/>
-    <col min="4" max="4" width="16.7109375" customWidth="1"/>
+    <col min="3" max="3" width="22.5" customWidth="1"/>
+    <col min="4" max="4" width="16.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="18" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>44</v>
       </c>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>45</v>
       </c>
       <c r="C2" s="2"/>
     </row>
-    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="3"/>
@@ -1918,7 +1961,7 @@
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
     </row>
-    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="2"/>
       <c r="B6" s="4"/>
       <c r="C6" s="5"/>
@@ -1927,7 +1970,7 @@
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
     </row>
-    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="2"/>
       <c r="B7" s="6"/>
       <c r="C7" s="7" t="s">
@@ -1938,7 +1981,7 @@
       <c r="F7" s="2"/>
       <c r="G7" s="2"/>
     </row>
-    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="2"/>
       <c r="B8" s="6"/>
       <c r="C8" s="7" t="s">
@@ -1949,7 +1992,7 @@
       <c r="F8" s="2"/>
       <c r="G8" s="2"/>
     </row>
-    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="2"/>
       <c r="B9" s="6"/>
       <c r="C9" s="7" t="s">
@@ -1960,7 +2003,7 @@
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
       <c r="B10" s="6"/>
       <c r="C10" s="7" t="s">
@@ -1971,7 +2014,7 @@
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
     </row>
-    <row r="11" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="9"/>
       <c r="C11" s="10"/>
@@ -1980,7 +2023,7 @@
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
     </row>
-    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="2"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
@@ -1989,7 +2032,7 @@
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
     </row>
-    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="2"/>
       <c r="B13" s="2"/>
       <c r="C13" s="3" t="s">
@@ -2000,7 +2043,7 @@
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="3"/>
@@ -2009,7 +2052,7 @@
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
     </row>
-    <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="2"/>
       <c r="B15" s="12"/>
       <c r="C15" s="13"/>
@@ -2018,7 +2061,7 @@
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
     </row>
-    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="2"/>
       <c r="B16" s="14"/>
       <c r="C16" s="15" t="s">
@@ -2029,7 +2072,7 @@
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
     </row>
-    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="2"/>
       <c r="B17" s="14"/>
       <c r="C17" s="15"/>
@@ -2038,7 +2081,7 @@
       <c r="F17" s="2"/>
       <c r="G17" s="2"/>
     </row>
-    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="2"/>
       <c r="B18" s="14"/>
       <c r="C18" s="15" t="s">
@@ -2049,7 +2092,7 @@
       <c r="F18" s="2"/>
       <c r="G18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
       <c r="B19" s="16"/>
       <c r="C19" s="17"/>
@@ -2058,7 +2101,7 @@
       <c r="F19" s="2"/>
       <c r="G19" s="2"/>
     </row>
-    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -2072,15 +2115,15 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30A98179-E3EF-4868-B4D4-F31FE6C0440E}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="51" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="105" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" ht="105" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="69" t="s">
         <v>54</v>
       </c>
@@ -2090,36 +2133,36 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{439BC25C-4D42-43C9-91E2-895C5EC26A0E}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="64.42578125" customWidth="1"/>
-    <col min="2" max="2" width="21.7109375" customWidth="1"/>
-    <col min="3" max="3" width="18.7109375" customWidth="1"/>
-    <col min="4" max="4" width="17.5703125" customWidth="1"/>
-    <col min="5" max="5" width="22.28515625" customWidth="1"/>
-    <col min="6" max="6" width="27.42578125" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" customWidth="1"/>
+    <col min="1" max="1" width="64.5" customWidth="1"/>
+    <col min="2" max="2" width="21.6640625" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" customWidth="1"/>
+    <col min="6" max="6" width="27.5" customWidth="1"/>
+    <col min="7" max="7" width="13.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="65" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A2" s="65" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="66" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>51</v>
       </c>
@@ -2128,7 +2171,7 @@
       <c r="D5" s="64"/>
       <c r="E5" s="64"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>52</v>
       </c>
@@ -2137,12 +2180,12 @@
       <c r="D6" s="64"/>
       <c r="E6" s="64"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="64" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="64" t="s">
         <v>47</v>
       </c>
